--- a/花境设计素材库/花境设计辅助工具_数据库.xlsx
+++ b/花境设计素材库/花境设计辅助工具_数据库.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\work\工作室——设计文件（研究学习的重要资料）\01个人文件\Twolobster 2026\花境设计辅助系统\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\work\工作室——设计文件（研究学习的重要资料）\01个人文件\Twolobster 2026\花境设计素材库\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2CE129-BA3F-45C8-830F-D05B1CB53497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49B257B-9807-4174-9F06-7E3349E2837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="538">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -681,10 +681,6 @@
   </si>
   <si>
     <t>f32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>粉、紫红</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2563,13 +2559,13 @@
         <v>77</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>18</v>
@@ -2599,7 +2595,7 @@
         <v>27</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>18</v>
@@ -2653,13 +2649,13 @@
         <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
@@ -2671,10 +2667,10 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>31</v>
@@ -2683,7 +2679,7 @@
         <v>77</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>22</v>
@@ -2701,10 +2697,10 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>32</v>
@@ -2713,13 +2709,13 @@
         <v>77</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="H8" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>18</v>
@@ -2731,10 +2727,10 @@
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>158</v>
@@ -2746,10 +2742,10 @@
         <v>164</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>18</v>
@@ -2761,10 +2757,10 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>158</v>
@@ -2779,7 +2775,7 @@
         <v>126</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>18</v>
@@ -2791,10 +2787,10 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>31</v>
@@ -2809,7 +2805,7 @@
         <v>13</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>18</v>
@@ -2821,10 +2817,10 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>93</v>
@@ -2836,25 +2832,25 @@
         <v>153</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>158</v>
@@ -2869,7 +2865,7 @@
         <v>13</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>18</v>
@@ -2881,10 +2877,10 @@
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>31</v>
@@ -2893,28 +2889,28 @@
         <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>455</v>
-      </c>
       <c r="H14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>31</v>
@@ -2923,13 +2919,13 @@
         <v>77</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>18</v>
@@ -2941,10 +2937,10 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
@@ -2953,28 +2949,28 @@
         <v>77</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>31</v>
@@ -2983,28 +2979,28 @@
         <v>77</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>474</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>32</v>
@@ -3016,7 +3012,7 @@
         <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>132</v>
@@ -3031,10 +3027,10 @@
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>31</v>
@@ -3043,13 +3039,13 @@
         <v>77</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>18</v>
@@ -3061,10 +3057,10 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>31</v>
@@ -3076,10 +3072,10 @@
         <v>105</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>18</v>
@@ -3360,7 +3356,7 @@
         <v>78</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>98</v>
@@ -3438,10 +3434,10 @@
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>31</v>
@@ -3450,28 +3446,28 @@
         <v>78</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G39" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="J39" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>31</v>
@@ -3486,7 +3482,7 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>18</v>
@@ -3498,10 +3494,10 @@
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>31</v>
@@ -3516,7 +3512,7 @@
         <v>140</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>18</v>
@@ -3528,10 +3524,10 @@
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>31</v>
@@ -3540,10 +3536,10 @@
         <v>78</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>124</v>
@@ -3558,10 +3554,10 @@
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>31</v>
@@ -3570,10 +3566,10 @@
         <v>78</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>124</v>
@@ -3732,7 +3728,7 @@
         <v>27</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>18</v>
@@ -3897,7 +3893,7 @@
         <v>119</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>31</v>
@@ -3987,7 +3983,7 @@
         <v>134</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>31</v>
@@ -4002,13 +3998,13 @@
         <v>133</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -4164,10 +4160,10 @@
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>31</v>
@@ -4179,7 +4175,7 @@
         <v>30</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>124</v>
@@ -4194,19 +4190,19 @@
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>79</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>84</v>
@@ -4224,10 +4220,10 @@
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>31</v>
@@ -4239,10 +4235,10 @@
         <v>102</v>
       </c>
       <c r="G70" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>18</v>
@@ -4254,10 +4250,10 @@
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>32</v>
@@ -4266,13 +4262,13 @@
         <v>79</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>18</v>
@@ -4284,10 +4280,10 @@
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>93</v>
@@ -4314,10 +4310,10 @@
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>158</v>
@@ -4326,7 +4322,7 @@
         <v>79</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>13</v>
@@ -4344,10 +4340,10 @@
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>31</v>
@@ -4374,10 +4370,10 @@
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>93</v>
@@ -4398,16 +4394,16 @@
         <v>18</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>31</v>
@@ -4416,7 +4412,7 @@
         <v>79</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>98</v>
@@ -4434,10 +4430,10 @@
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>31</v>
@@ -4446,7 +4442,7 @@
         <v>79</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>126</v>
@@ -4464,7 +4460,7 @@
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>163</v>
@@ -4494,10 +4490,10 @@
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>31</v>
@@ -4506,10 +4502,10 @@
         <v>79</v>
       </c>
       <c r="F79" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>29</v>
@@ -4524,10 +4520,10 @@
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>32</v>
@@ -4554,10 +4550,10 @@
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>32</v>
@@ -4569,13 +4565,13 @@
         <v>125</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>15</v>
@@ -4584,10 +4580,10 @@
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>31</v>
@@ -4596,28 +4592,28 @@
         <v>79</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G82" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="I82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>32</v>
@@ -4626,10 +4622,10 @@
         <v>79</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>5</v>
@@ -4644,10 +4640,10 @@
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>32</v>
@@ -4674,10 +4670,10 @@
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>31</v>
@@ -4689,10 +4685,10 @@
         <v>164</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>18</v>
@@ -4704,10 +4700,10 @@
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>31</v>
@@ -4716,13 +4712,13 @@
         <v>79</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>18</v>
@@ -4734,10 +4730,10 @@
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>31</v>
@@ -4749,7 +4745,7 @@
         <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>25</v>
@@ -4764,10 +4760,10 @@
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>31</v>
@@ -4779,7 +4775,7 @@
         <v>153</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>123</v>
@@ -4788,16 +4784,16 @@
         <v>18</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>31</v>
@@ -4824,10 +4820,10 @@
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>32</v>
@@ -4839,7 +4835,7 @@
         <v>102</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>5</v>
@@ -4854,10 +4850,10 @@
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>31</v>
@@ -4884,10 +4880,10 @@
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>32</v>
@@ -4914,10 +4910,10 @@
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>31</v>
@@ -4944,10 +4940,10 @@
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>93</v>
@@ -4956,25 +4952,25 @@
         <v>79</v>
       </c>
       <c r="F94" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>71</v>
@@ -4989,7 +4985,7 @@
         <v>7</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>21</v>
@@ -5051,7 +5047,7 @@
         <v>120</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>31</v>
@@ -5198,10 +5194,10 @@
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>158</v>
@@ -5210,13 +5206,13 @@
         <v>80</v>
       </c>
       <c r="F103" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>18</v>
@@ -5228,10 +5224,10 @@
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>31</v>
@@ -5240,13 +5236,13 @@
         <v>80</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>18</v>
@@ -5258,10 +5254,10 @@
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>158</v>
@@ -5276,7 +5272,7 @@
         <v>27</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>18</v>
@@ -5288,10 +5284,10 @@
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>158</v>
@@ -5300,13 +5296,13 @@
         <v>80</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>18</v>
@@ -5318,7 +5314,7 @@
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>82</v>
@@ -5330,7 +5326,7 @@
         <v>80</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>140</v>
@@ -5348,7 +5344,7 @@
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>73</v>
@@ -5360,25 +5356,25 @@
         <v>80</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>74</v>
@@ -5396,22 +5392,22 @@
         <v>13</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>158</v>
@@ -5420,13 +5416,13 @@
         <v>80</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>18</v>
@@ -5438,10 +5434,10 @@
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>31</v>
@@ -5450,10 +5446,10 @@
         <v>80</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>90</v>
@@ -5468,22 +5464,22 @@
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="D112" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>139</v>
@@ -5498,10 +5494,10 @@
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>93</v>
@@ -5513,10 +5509,10 @@
         <v>105</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>18</v>
@@ -5528,10 +5524,10 @@
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>31</v>
@@ -5540,7 +5536,7 @@
         <v>80</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>13</v>
@@ -5549,7 +5545,7 @@
         <v>139</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J114" s="3" t="s">
         <v>92</v>
@@ -5558,10 +5554,10 @@
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>31</v>
@@ -5603,7 +5599,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -5673,7 +5669,7 @@
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -5721,7 +5717,7 @@
         <v>38</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J124" s="3" t="s">
         <v>90</v>
@@ -5730,10 +5726,10 @@
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>31</v>
@@ -5742,16 +5738,16 @@
         <v>81</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>123</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>5</v>
@@ -5760,10 +5756,10 @@
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>31</v>
@@ -5784,16 +5780,16 @@
         <v>18</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>31</v>
@@ -5802,16 +5798,16 @@
         <v>81</v>
       </c>
       <c r="F127" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="G127" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="G127" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>5</v>
@@ -5820,10 +5816,10 @@
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>31</v>
@@ -5832,16 +5828,16 @@
         <v>81</v>
       </c>
       <c r="F128" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="I128" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J128" s="3" t="s">
         <v>5</v>
@@ -5850,13 +5846,13 @@
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E129" s="15" t="s">
         <v>81</v>
@@ -5865,13 +5861,13 @@
         <v>116</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>5</v>
@@ -5880,10 +5876,10 @@
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>31</v>
@@ -5892,28 +5888,28 @@
         <v>81</v>
       </c>
       <c r="F130" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="G130" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="H130" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="I130" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J130" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="I130" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>31</v>
@@ -5922,16 +5918,16 @@
         <v>81</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G131" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H131" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="I131" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J131" s="3" t="s">
         <v>5</v>
@@ -6077,7 +6073,7 @@
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B144" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>20</v>
@@ -6089,7 +6085,7 @@
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B145" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>24</v>
@@ -6101,7 +6097,7 @@
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B146" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>28</v>
@@ -6111,7 +6107,7 @@
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B147" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>34</v>
@@ -6120,7 +6116,7 @@
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B148" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>37</v>
@@ -6128,7 +6124,7 @@
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B149" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>83</v>
@@ -6136,7 +6132,7 @@
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B150" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>89</v>
@@ -6144,7 +6140,7 @@
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B151" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>95</v>
@@ -6152,7 +6148,7 @@
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B152" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>100</v>
@@ -6160,7 +6156,7 @@
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B153" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>104</v>
@@ -6168,7 +6164,7 @@
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B154" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>72</v>
@@ -6176,7 +6172,7 @@
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B155" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>107</v>
@@ -6184,7 +6180,7 @@
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B156" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>111</v>
@@ -6192,7 +6188,7 @@
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B157" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>115</v>
@@ -6200,23 +6196,23 @@
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B158" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B159" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B160" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>121</v>
@@ -6224,7 +6220,7 @@
     </row>
     <row r="161" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B161" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>128</v>
@@ -6232,7 +6228,7 @@
     </row>
     <row r="162" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B162" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>10</v>
@@ -6240,15 +6236,15 @@
     </row>
     <row r="163" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B163" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="164" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B164" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>135</v>
@@ -6256,7 +6252,7 @@
     </row>
     <row r="165" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B165" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>75</v>
@@ -6264,7 +6260,7 @@
     </row>
     <row r="166" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B166" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>142</v>
@@ -6272,7 +6268,7 @@
     </row>
     <row r="167" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B167" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>145</v>
@@ -6280,7 +6276,7 @@
     </row>
     <row r="168" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B168" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>148</v>
@@ -6288,7 +6284,7 @@
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B169" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>151</v>
@@ -6296,7 +6292,7 @@
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B170" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>155</v>
@@ -6304,7 +6300,7 @@
     </row>
     <row r="171" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B171" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>157</v>
@@ -6312,7 +6308,7 @@
     </row>
     <row r="172" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B172" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>161</v>
@@ -6320,7 +6316,7 @@
     </row>
     <row r="173" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B173" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>168</v>
@@ -6328,7 +6324,7 @@
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B174" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>170</v>
@@ -6336,159 +6332,159 @@
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B175" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B176" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="177" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B177" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="178" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B178" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B179" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B180" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B181" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="182" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B182" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="183" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B183" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="184" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B184" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="185" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B185" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="186" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B186" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B187" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="188" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B188" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="189" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B189" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="190" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B190" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="191" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B191" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="192" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B192" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B193" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="194" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B194" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>163</v>
@@ -6496,15 +6492,15 @@
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B195" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="196" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B196" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>82</v>
@@ -6512,23 +6508,23 @@
     </row>
     <row r="197" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B197" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="198" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B198" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="199" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B199" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>73</v>
@@ -6536,7 +6532,7 @@
     </row>
     <row r="200" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B200" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>74</v>
@@ -6544,287 +6540,287 @@
     </row>
     <row r="201" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B201" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B202" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="203" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B203" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="204" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B204" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="205" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B205" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="206" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B206" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="207" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B207" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B208" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="209" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B209" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="210" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B210" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="211" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B211" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="212" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B212" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="213" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B213" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C213" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="214" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B214" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C214" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="215" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B215" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C215" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="216" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B216" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="217" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B217" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="218" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B218" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="219" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B219" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="220" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B220" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="221" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B221" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="222" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B222" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="223" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B223" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="224" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B224" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="225" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B225" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="226" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B226" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B227" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="228" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B228" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="229" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B229" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="230" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B230" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B231" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="232" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="233" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B233" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B234" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B235" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="236" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B236" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>71</v>
@@ -6832,47 +6828,47 @@
     </row>
     <row r="237" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B237" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="238" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B238" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="239" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B239" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B240" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="241" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B241" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="242" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B242" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -6892,33 +6888,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="C1" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="F1" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="G1" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>512</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>37</v>
@@ -6927,13 +6923,13 @@
         <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>20</v>
@@ -6944,21 +6940,21 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>89</v>
@@ -6966,13 +6962,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>142</v>
@@ -6980,22 +6976,22 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -7006,21 +7002,21 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -7029,13 +7025,13 @@
         <v>75</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>135</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -7046,21 +7042,21 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H8" s="1"/>
     </row>
@@ -7069,10 +7065,10 @@
         <v>73</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>168</v>
@@ -7086,13 +7082,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>170</v>
@@ -7106,16 +7102,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -7124,16 +7120,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -7142,13 +7138,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -7158,10 +7154,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
@@ -7175,7 +7171,7 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>161</v>
@@ -7189,10 +7185,10 @@
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -7203,10 +7199,10 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -7217,10 +7213,10 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
